--- a/artfynd/A 25142-2026 artfynd.xlsx
+++ b/artfynd/A 25142-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134242933</v>
       </c>
       <c r="B2" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>134242954</v>
       </c>
       <c r="B5" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>134242935</v>
       </c>
       <c r="B6" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>134242930</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>134242953</v>
       </c>
       <c r="B8" t="n">
-        <v>102301</v>
+        <v>102303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>134242945</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>134242951</v>
       </c>
       <c r="B10" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>134242926</v>
       </c>
       <c r="B11" t="n">
-        <v>92228</v>
+        <v>92230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>134242943</v>
       </c>
       <c r="B12" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>134242925</v>
       </c>
       <c r="B13" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>134242937</v>
       </c>
       <c r="B14" t="n">
-        <v>99095</v>
+        <v>99097</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>134242946</v>
       </c>
       <c r="B15" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>134242950</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>134242948</v>
       </c>
       <c r="B17" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134242928</v>
+        <v>134242959</v>
       </c>
       <c r="B18" t="n">
         <v>57975</v>
@@ -2466,7 +2466,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566323</v>
+        <v>566249</v>
       </c>
       <c r="R18" t="n">
-        <v>6934317</v>
+        <v>6934245</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,7 +2553,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134242959</v>
+        <v>134242928</v>
       </c>
       <c r="B19" t="n">
         <v>57975</v>
@@ -2586,7 +2586,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566249</v>
+        <v>566323</v>
       </c>
       <c r="R19" t="n">
-        <v>6934245</v>
+        <v>6934317</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2796,7 +2796,7 @@
         <v>134242952</v>
       </c>
       <c r="B21" t="n">
-        <v>99095</v>
+        <v>99097</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>134242942</v>
       </c>
       <c r="B22" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>134242947</v>
       </c>
       <c r="B23" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>134242944</v>
       </c>
       <c r="B24" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>134242939</v>
       </c>
       <c r="B25" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>134242957</v>
       </c>
       <c r="B26" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>134242940</v>
       </c>
       <c r="B27" t="n">
-        <v>97291</v>
+        <v>97293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>134242941</v>
       </c>
       <c r="B29" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>134242927</v>
       </c>
       <c r="B30" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 25142-2026 artfynd.xlsx
+++ b/artfynd/A 25142-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242926</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242925</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242956</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242927</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242940</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242955</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242923</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242930</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242939</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242942</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242945</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242951</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242935</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242948</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2290,6 +2365,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242924</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2410,6 +2490,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242928</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2530,6 +2615,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242929</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2650,6 +2740,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242934</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2770,6 +2865,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242958</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2890,6 +2990,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242959</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2997,6 +3102,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242937</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3104,6 +3214,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242952</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3216,6 +3331,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242933</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3328,6 +3448,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242943</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3440,6 +3565,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242944</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3552,6 +3682,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242946</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3664,6 +3799,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242947</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3776,6 +3916,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242954</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3888,6 +4033,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242957</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3995,6 +4145,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242953</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4102,6 +4257,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242941</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4209,6 +4369,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242936</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4316,8 +4481,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134242950</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>